--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42434-2026 artfynd.xlsx
+++ b/artfynd/A 42434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282843</v>
       </c>
       <c r="B2" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
